--- a/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
+++ b/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T13:33:30+00:00</t>
+    <t>2024-11-06T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
+++ b/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T15:55:45+00:00</t>
+    <t>2024-11-26T12:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
+++ b/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T12:51:17+00:00</t>
+    <t>2024-11-26T14:12:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
+++ b/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T14:12:54+00:00</t>
+    <t>2024-12-02T10:46:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
+++ b/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T10:46:43+00:00</t>
+    <t>2024-12-02T16:50:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
+++ b/ig/improve-doc/ASS-X15-AgregatDisciplineEnseignement.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T16:50:25+00:00</t>
+    <t>2024-12-04T07:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
